--- a/TABLA_RESUMEN_CYPS.xlsx
+++ b/TABLA_RESUMEN_CYPS.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23010" windowHeight="9015"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -76,7 +76,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.000000000"/>
+    <numFmt numFmtId="164" formatCode="0.000000000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -107,12 +107,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -123,9 +138,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -495,7 +510,7 @@
         <v>5</v>
       </c>
       <c r="H3" s="2">
-        <v>0.55205460000000017</v>
+        <v>0.55235460000000014</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -576,7 +591,7 @@
         <v>18</v>
       </c>
       <c r="H6" s="5">
-        <v>3.58746E-2</v>
+        <v>3.6649350000000004E-2</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -603,7 +618,7 @@
         <v>4</v>
       </c>
       <c r="H7" s="3">
-        <v>14.076952326800001</v>
+        <v>14.074579040234442</v>
       </c>
       <c r="I7" s="3"/>
     </row>
@@ -629,7 +644,7 @@
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H9">
         <f>SUM(H2:H8)</f>
-        <v>14.873810866800001</v>
+        <v>14.872512330234441</v>
       </c>
     </row>
   </sheetData>

--- a/TABLA_RESUMEN_CYPS.xlsx
+++ b/TABLA_RESUMEN_CYPS.xlsx
@@ -510,7 +510,7 @@
         <v>5</v>
       </c>
       <c r="H3" s="2">
-        <v>0.55235460000000014</v>
+        <v>0.55235460000000003</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -537,7 +537,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="2">
-        <v>0</v>
+        <v>2.4000000000000001E-4</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -564,7 +564,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="2">
-        <v>2.2712740000000002E-2</v>
+        <v>3.1666739999999999E-2</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -591,7 +591,7 @@
         <v>18</v>
       </c>
       <c r="H6" s="5">
-        <v>3.6649350000000004E-2</v>
+        <v>3.4952499999999997E-2</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -618,7 +618,7 @@
         <v>4</v>
       </c>
       <c r="H7" s="3">
-        <v>14.074579040234442</v>
+        <v>20.05115584</v>
       </c>
       <c r="I7" s="3"/>
     </row>
@@ -644,7 +644,7 @@
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H9">
         <f>SUM(H2:H8)</f>
-        <v>14.872512330234441</v>
+        <v>20.856586279999998</v>
       </c>
     </row>
   </sheetData>

--- a/TABLA_RESUMEN_CYPS.xlsx
+++ b/TABLA_RESUMEN_CYPS.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Fobos\Proyecto_Diana\TFM_GenoStaR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\ctoma\Fobos\Proyecto_Diana\TFM_GenoStaR\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>CYP</t>
   </si>
@@ -65,10 +65,7 @@
     <t xml:space="preserve">Error rs solo genostar </t>
   </si>
   <si>
-    <t xml:space="preserve">nº *alelos no tenidos en cuenta en genostar </t>
-  </si>
-  <si>
-    <t>nº *alelos sin frec poblacional de los *alelos no tenidos en cuenta en genostar</t>
+    <t>Call rate genostar</t>
   </si>
 </sst>
 </file>
@@ -87,47 +84,20 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -137,10 +107,10 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -421,19 +391,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="14.5703125" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" customWidth="1"/>
-    <col min="8" max="8" width="19.28515625" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -446,20 +414,17 @@
       <c r="D1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -476,17 +441,14 @@
       <c r="E2">
         <v>24</v>
       </c>
-      <c r="F2" s="2">
-        <v>24</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1</v>
-      </c>
-      <c r="H2" s="2">
+      <c r="F2" s="1">
         <v>0.18621659999999998</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -503,17 +465,14 @@
       <c r="E3">
         <v>24</v>
       </c>
-      <c r="F3" s="2">
-        <v>24</v>
+      <c r="F3" s="1">
+        <v>0.55235460000000003</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0.55235460000000003</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>99.39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -530,17 +489,14 @@
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="F4" s="2">
-        <v>1</v>
+      <c r="F4" s="1">
+        <v>2.4000000000000001E-4</v>
       </c>
       <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2">
-        <v>2.4000000000000001E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -557,17 +513,14 @@
       <c r="E5">
         <v>11</v>
       </c>
-      <c r="F5" s="2">
-        <v>12</v>
+      <c r="F5" s="1">
+        <v>3.1666739999999999E-2</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5" s="2">
-        <v>3.1666739999999999E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>32.729999999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -584,17 +537,14 @@
       <c r="E6">
         <v>39</v>
       </c>
-      <c r="F6" s="2">
-        <v>39</v>
+      <c r="F6" s="5">
+        <v>3.4952499999999997E-2</v>
       </c>
       <c r="G6">
-        <v>18</v>
-      </c>
-      <c r="H6" s="5">
-        <v>3.4952499999999997E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>98.94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -612,17 +562,13 @@
         <v>18</v>
       </c>
       <c r="F7" s="2">
-        <v>21</v>
-      </c>
-      <c r="G7" s="2">
-        <v>4</v>
-      </c>
-      <c r="H7" s="3">
         <v>20.05115584</v>
       </c>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G7" s="4">
+        <v>96.06</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -639,11 +585,14 @@
       <c r="E8">
         <v>110</v>
       </c>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="H9">
-        <f>SUM(H2:H8)</f>
+      <c r="F8" s="1"/>
+      <c r="G8">
+        <v>47.58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F9">
+        <f>SUM(F2:F8)</f>
         <v>20.856586279999998</v>
       </c>
     </row>
